--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -1,40 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010BB5BA-65C0-4F9D-A83F-CF7F2E6556F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2835" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>Player Name</t>
+  </si>
+  <si>
+    <t>CMJ 1</t>
+  </si>
+  <si>
+    <t>CMJ 2</t>
+  </si>
+  <si>
+    <t>Abby Buys</t>
+  </si>
+  <si>
+    <t>Abby Wright</t>
+  </si>
+  <si>
+    <t>Ava Heil</t>
+  </si>
+  <si>
+    <t>Beatrice Levi</t>
+  </si>
+  <si>
+    <t>Cameron Simmons</t>
+  </si>
+  <si>
+    <t>Emma Blakely</t>
+  </si>
+  <si>
+    <t>Emma Naftzger</t>
+  </si>
+  <si>
+    <t>Gianna Masinter</t>
+  </si>
+  <si>
+    <t>Grace Nelson</t>
+  </si>
+  <si>
+    <t>Hannah Boelscher</t>
+  </si>
+  <si>
+    <t>Hayley "Lehua" Hanawahine</t>
+  </si>
+  <si>
+    <t>Jade Vacheck</t>
+  </si>
+  <si>
+    <t>Jenna Bisset</t>
+  </si>
+  <si>
+    <t>Juliet Thrapp</t>
+  </si>
+  <si>
+    <t>Kaleia Coughlin</t>
+  </si>
+  <si>
+    <t>Kody McKinney</t>
+  </si>
+  <si>
+    <t>Kylee Jerome</t>
+  </si>
+  <si>
+    <t>Leah Uezato</t>
+  </si>
+  <si>
+    <t>Lila Jones</t>
+  </si>
+  <si>
+    <t>Madelyn Saruwatari</t>
+  </si>
+  <si>
+    <t>Madilyn Audet</t>
+  </si>
+  <si>
+    <t>Madison Khan</t>
+  </si>
+  <si>
+    <t>Molly Bachman</t>
+  </si>
+  <si>
+    <t>Nicole Ross</t>
+  </si>
+  <si>
+    <t>Priya Torres</t>
+  </si>
+  <si>
+    <t>Riley Johnson</t>
+  </si>
+  <si>
+    <t>Shaylen Greff</t>
+  </si>
+  <si>
+    <t>Tessa Anastasi</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +159,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -424,1050 +484,901 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Match</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Player Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CMJ 1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CMJ 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>46255</v>
       </c>
       <c r="B2" t="b">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Abby Buys</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
         <v>14.5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>14.5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>46255</v>
       </c>
       <c r="B3" t="b">
         <v>0</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Abby Wright</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3">
         <v>13</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>12.7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>46255</v>
       </c>
       <c r="B4" t="b">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ava Heil</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
         <v>13.4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>13.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>46255</v>
       </c>
       <c r="B5" t="b">
         <v>0</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Beatrice Levi</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
         <v>11.6</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>11.8</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46255</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Cameron Simmons</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
         <v>9.9</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>10.1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>46255</v>
       </c>
       <c r="B7" t="b">
         <v>0</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Emma Blakely</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>46255</v>
       </c>
       <c r="B8" t="b">
         <v>0</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Emma Naftzger</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
         <v>14.7</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>14.8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>46255</v>
       </c>
       <c r="B9" t="b">
         <v>0</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Gianna Masinter</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9">
         <v>9.6</v>
       </c>
-      <c r="E9" t="n">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="E9">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>46255</v>
       </c>
       <c r="B10" t="b">
         <v>0</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Grace Nelson</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
         <v>13.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>14.1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>46255</v>
       </c>
       <c r="B11" t="b">
         <v>0</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Hannah Boelscher</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
         <v>12.7</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>12.7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>46255</v>
       </c>
       <c r="B12" t="b">
         <v>0</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Hayley "Lehua" Hanawahine</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
         <v>13.1</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>13.2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>46255</v>
       </c>
       <c r="B13" t="b">
         <v>0</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Jade Vacheck</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13">
         <v>13.1</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>13.2</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>46255</v>
       </c>
       <c r="B14" t="b">
         <v>0</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Jenna Bisset</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14">
         <v>12.5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>11.7</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>46255</v>
       </c>
       <c r="B15" t="b">
         <v>0</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Juliet Thrapp</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>46255</v>
       </c>
       <c r="B16" t="b">
         <v>0</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Kaleia Coughlin</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
         <v>10.1</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>10.8</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>46255</v>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Kody McKinney</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17">
         <v>12.1</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>12.5</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>46255</v>
       </c>
       <c r="B18" t="b">
         <v>0</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Kylee Jerome</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>46255</v>
       </c>
       <c r="B19" t="b">
         <v>0</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Leah Uezato</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19">
         <v>9.9</v>
       </c>
-      <c r="E19" t="n">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="E19">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>46255</v>
       </c>
       <c r="B20" t="b">
         <v>0</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Lila Jones</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20">
         <v>14.1</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>14.3</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>46255</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Madelyn Saruwatari</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>46255</v>
       </c>
       <c r="B22" t="b">
         <v>0</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Madilyn Audet</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>46255</v>
       </c>
       <c r="B23" t="b">
         <v>0</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Madison Khan</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>46255</v>
       </c>
       <c r="B24" t="b">
         <v>0</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Molly Bachman</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
+      <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24">
         <v>13.1</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>13.5</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>46255</v>
       </c>
       <c r="B25" t="b">
         <v>0</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nicole Ross</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25">
         <v>14.8</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>14.5</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>46255</v>
       </c>
       <c r="B26" t="b">
         <v>0</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Priya Torres</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
         <v>12.3</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>12.2</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>46255</v>
       </c>
       <c r="B27" t="b">
         <v>0</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Riley Johnson</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27">
         <v>12.1</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>12.3</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>46255</v>
       </c>
       <c r="B28" t="b">
         <v>0</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Shaylen Greff</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28">
         <v>13</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>12.8</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>46255</v>
       </c>
       <c r="B29" t="b">
         <v>0</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Tessa Anastasi</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29">
         <v>12</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>11.6</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>46256</v>
       </c>
       <c r="B30" t="b">
         <v>1</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Abby Buys</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30">
         <v>16.3</v>
       </c>
-      <c r="E30" t="n">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="E30">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>46256</v>
       </c>
       <c r="B31" t="b">
         <v>1</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Abby Wright</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31">
         <v>14.8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>15</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>46256</v>
       </c>
       <c r="B32" t="b">
         <v>1</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ava Heil</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32">
         <v>13.8</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>14.3</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>46256</v>
       </c>
       <c r="B33" t="b">
         <v>1</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Beatrice Levi</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33">
         <v>13.6</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>14.2</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>46256</v>
       </c>
       <c r="B34" t="b">
         <v>1</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Cameron Simmons</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34">
         <v>11.6</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>10.6</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>46256</v>
       </c>
       <c r="B35" t="b">
         <v>1</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Emma Blakely</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>46256</v>
       </c>
       <c r="B36" t="b">
         <v>1</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Emma Naftzger</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36">
         <v>16.5</v>
       </c>
-      <c r="E36" t="n">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="E36">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>46256</v>
       </c>
       <c r="B37" t="b">
         <v>1</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Gianna Masinter</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37">
         <v>10.8</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>11.8</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>46256</v>
       </c>
       <c r="B38" t="b">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Grace Nelson</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38">
         <v>14.7</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>15</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>46256</v>
       </c>
       <c r="B39" t="b">
         <v>1</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Hannah Boelscher</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39">
         <v>13.5</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>13.2</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>46256</v>
       </c>
       <c r="B40" t="b">
         <v>1</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Hayley "Lehua" Hanawahine</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>46256</v>
       </c>
       <c r="B41" t="b">
         <v>1</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Jade Vacheck</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41">
         <v>14.2</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>14.4</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>46256</v>
       </c>
       <c r="B42" t="b">
         <v>1</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Jenna Bisset</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42">
         <v>14.4</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>15</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>46256</v>
       </c>
       <c r="B43" t="b">
         <v>1</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Juliet Thrapp</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="C43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>46256</v>
       </c>
       <c r="B44" t="b">
         <v>1</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Kaleia Coughlin</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44">
         <v>11.8</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>11.2</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
         <v>46256</v>
       </c>
       <c r="B45" t="b">
         <v>1</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Kody McKinney</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45">
         <v>13.3</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>13.7</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>46256</v>
       </c>
       <c r="B46" t="b">
         <v>1</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Kylee Jerome</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="C46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
         <v>46256</v>
       </c>
       <c r="B47" t="b">
         <v>1</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Leah Uezato</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47">
         <v>12.1</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>12.6</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <v>46256</v>
       </c>
       <c r="B48" t="b">
         <v>1</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Lila Jones</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48">
         <v>14.1</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>15</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
         <v>46256</v>
       </c>
       <c r="B49" t="b">
         <v>1</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Madelyn Saruwatari</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
         <v>46256</v>
       </c>
       <c r="B50" t="b">
         <v>1</v>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Madilyn Audet</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="C50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
         <v>46256</v>
       </c>
       <c r="B51" t="b">
         <v>1</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Madison Khan</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="C51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <v>46256</v>
       </c>
       <c r="B52" t="b">
         <v>1</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Molly Bachman</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52">
         <v>15</v>
       </c>
-      <c r="E52" t="n">
-        <v>16.6</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="E52">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
         <v>46256</v>
       </c>
       <c r="B53" t="b">
         <v>1</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nicole Ross</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="C53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E53">
         <v>17</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
         <v>46256</v>
       </c>
       <c r="B54" t="b">
         <v>1</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Priya Torres</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
+      <c r="C54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54">
         <v>11.6</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>13.4</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
         <v>46256</v>
       </c>
       <c r="B55" t="b">
         <v>1</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Riley Johnson</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
+      <c r="C55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55">
         <v>13.8</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>14.1</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
         <v>46256</v>
       </c>
       <c r="B56" t="b">
         <v>1</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Shaylen Greff</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56">
         <v>12.3</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>13.1</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
         <v>46256</v>
       </c>
       <c r="B57" t="b">
         <v>1</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tessa Anastasi</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
+      <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57">
         <v>12</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>12.6</v>
       </c>
     </row>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010BB5BA-65C0-4F9D-A83F-CF7F2E6556F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C50F9FF-9E33-45DC-9E3A-8C6C91C1E722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2835" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -126,7 +126,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -182,7 +182,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,10 +485,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1382,6 +1383,467 @@
         <v>12.6</v>
       </c>
     </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B58" t="b">
+        <v>0</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58">
+        <v>15.2</v>
+      </c>
+      <c r="E58">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B59" t="b">
+        <v>0</v>
+      </c>
+      <c r="C59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59">
+        <v>12.6</v>
+      </c>
+      <c r="E59">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B60" t="b">
+        <v>0</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60">
+        <v>14.6</v>
+      </c>
+      <c r="E60">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B61" t="b">
+        <v>0</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61">
+        <v>13.7</v>
+      </c>
+      <c r="E61">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B62" t="b">
+        <v>0</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62">
+        <v>10.7</v>
+      </c>
+      <c r="E62">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B63" t="b">
+        <v>0</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B64" t="b">
+        <v>0</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64">
+        <v>15.3</v>
+      </c>
+      <c r="E64">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B65" t="b">
+        <v>0</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65">
+        <v>10.6</v>
+      </c>
+      <c r="E65">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B66" t="b">
+        <v>0</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66">
+        <v>13.7</v>
+      </c>
+      <c r="E66">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B67" t="b">
+        <v>0</v>
+      </c>
+      <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67">
+        <v>12.8</v>
+      </c>
+      <c r="E67">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B68" t="b">
+        <v>0</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68">
+        <v>12.8</v>
+      </c>
+      <c r="E68">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B69" t="b">
+        <v>0</v>
+      </c>
+      <c r="C69" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69">
+        <v>14.9</v>
+      </c>
+      <c r="E69">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B70" t="b">
+        <v>0</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70">
+        <v>12.9</v>
+      </c>
+      <c r="E70">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B71" t="b">
+        <v>0</v>
+      </c>
+      <c r="C71" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71">
+        <v>13.5</v>
+      </c>
+      <c r="E71">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B72" t="b">
+        <v>0</v>
+      </c>
+      <c r="C72" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72">
+        <v>12.2</v>
+      </c>
+      <c r="E72">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B73" t="b">
+        <v>0</v>
+      </c>
+      <c r="C73" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73">
+        <v>12.8</v>
+      </c>
+      <c r="E73">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B74" t="b">
+        <v>0</v>
+      </c>
+      <c r="C74" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B75" t="b">
+        <v>0</v>
+      </c>
+      <c r="C75" t="s">
+        <v>22</v>
+      </c>
+      <c r="D75">
+        <v>11.6</v>
+      </c>
+      <c r="E75">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B76" t="b">
+        <v>0</v>
+      </c>
+      <c r="C76" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76">
+        <v>14.9</v>
+      </c>
+      <c r="E76">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B77" t="b">
+        <v>0</v>
+      </c>
+      <c r="C77" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77">
+        <v>13.5</v>
+      </c>
+      <c r="E77">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B78" t="b">
+        <v>0</v>
+      </c>
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B79" t="b">
+        <v>0</v>
+      </c>
+      <c r="C79" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79">
+        <v>13.2</v>
+      </c>
+      <c r="E79">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B80" t="b">
+        <v>0</v>
+      </c>
+      <c r="C80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80">
+        <v>15.6</v>
+      </c>
+      <c r="E80">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B81" t="b">
+        <v>0</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81">
+        <v>15.2</v>
+      </c>
+      <c r="E81">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B82" t="b">
+        <v>0</v>
+      </c>
+      <c r="C82" t="s">
+        <v>29</v>
+      </c>
+      <c r="D82">
+        <v>13.8</v>
+      </c>
+      <c r="E82">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B83" t="b">
+        <v>0</v>
+      </c>
+      <c r="C83" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83">
+        <v>12.9</v>
+      </c>
+      <c r="E83">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B84" t="b">
+        <v>0</v>
+      </c>
+      <c r="C84" t="s">
+        <v>31</v>
+      </c>
+      <c r="D84">
+        <v>12.2</v>
+      </c>
+      <c r="E84">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B85" t="b">
+        <v>0</v>
+      </c>
+      <c r="C85" t="s">
+        <v>32</v>
+      </c>
+      <c r="D85">
+        <v>11.9</v>
+      </c>
+      <c r="E85">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C50F9FF-9E33-45DC-9E3A-8C6C91C1E722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EC696A-D114-477C-97A9-F988F8CF24A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7155" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -485,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1842,7 +1855,468 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="2"/>
+      <c r="A86" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B86" t="b">
+        <v>0</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86">
+        <v>16.5</v>
+      </c>
+      <c r="E86">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B87" t="b">
+        <v>0</v>
+      </c>
+      <c r="C87" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87">
+        <v>13</v>
+      </c>
+      <c r="E87">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B88" t="b">
+        <v>0</v>
+      </c>
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88">
+        <v>15.5</v>
+      </c>
+      <c r="E88">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B89" t="b">
+        <v>0</v>
+      </c>
+      <c r="C89" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89">
+        <v>12.7</v>
+      </c>
+      <c r="E89">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B90" t="b">
+        <v>0</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90">
+        <v>11.4</v>
+      </c>
+      <c r="E90">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B91" t="b">
+        <v>0</v>
+      </c>
+      <c r="C91" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B92" t="b">
+        <v>0</v>
+      </c>
+      <c r="C92" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92">
+        <v>14.4</v>
+      </c>
+      <c r="E92">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B93" t="b">
+        <v>0</v>
+      </c>
+      <c r="C93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93">
+        <v>10.4</v>
+      </c>
+      <c r="E93">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B94" t="b">
+        <v>0</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94">
+        <v>15.3</v>
+      </c>
+      <c r="E94">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B95" t="b">
+        <v>0</v>
+      </c>
+      <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95">
+        <v>13.4</v>
+      </c>
+      <c r="E95">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B96" t="b">
+        <v>0</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96">
+        <v>13</v>
+      </c>
+      <c r="E96">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B97" t="b">
+        <v>0</v>
+      </c>
+      <c r="C97" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97">
+        <v>14.2</v>
+      </c>
+      <c r="E97">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B98" t="b">
+        <v>0</v>
+      </c>
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98">
+        <v>13.3</v>
+      </c>
+      <c r="E98">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B99" t="b">
+        <v>0</v>
+      </c>
+      <c r="C99" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99">
+        <v>13.3</v>
+      </c>
+      <c r="E99">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B100" t="b">
+        <v>0</v>
+      </c>
+      <c r="C100" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100">
+        <v>12.5</v>
+      </c>
+      <c r="E100">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B101" t="b">
+        <v>0</v>
+      </c>
+      <c r="C101" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101">
+        <v>13</v>
+      </c>
+      <c r="E101">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B102" t="b">
+        <v>0</v>
+      </c>
+      <c r="C102" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102">
+        <v>15.5</v>
+      </c>
+      <c r="E102">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B103" t="b">
+        <v>0</v>
+      </c>
+      <c r="C103" t="s">
+        <v>22</v>
+      </c>
+      <c r="D103">
+        <v>11.3</v>
+      </c>
+      <c r="E103">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B104" t="b">
+        <v>0</v>
+      </c>
+      <c r="C104" t="s">
+        <v>23</v>
+      </c>
+      <c r="D104">
+        <v>14</v>
+      </c>
+      <c r="E104">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B105" t="b">
+        <v>0</v>
+      </c>
+      <c r="C105" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105">
+        <v>12.6</v>
+      </c>
+      <c r="E105">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B106" t="b">
+        <v>0</v>
+      </c>
+      <c r="C106" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B107" t="b">
+        <v>0</v>
+      </c>
+      <c r="C107" t="s">
+        <v>26</v>
+      </c>
+      <c r="D107">
+        <v>15.2</v>
+      </c>
+      <c r="E107">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B108" t="b">
+        <v>0</v>
+      </c>
+      <c r="C108" t="s">
+        <v>27</v>
+      </c>
+      <c r="D108">
+        <v>15.4</v>
+      </c>
+      <c r="E108">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B109" t="b">
+        <v>0</v>
+      </c>
+      <c r="C109" t="s">
+        <v>28</v>
+      </c>
+      <c r="D109">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E109">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B110" t="b">
+        <v>0</v>
+      </c>
+      <c r="C110" t="s">
+        <v>29</v>
+      </c>
+      <c r="D110">
+        <v>12.6</v>
+      </c>
+      <c r="E110">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B111" t="b">
+        <v>0</v>
+      </c>
+      <c r="C111" t="s">
+        <v>30</v>
+      </c>
+      <c r="D111">
+        <v>13</v>
+      </c>
+      <c r="E111">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B112" t="b">
+        <v>0</v>
+      </c>
+      <c r="C112" t="s">
+        <v>31</v>
+      </c>
+      <c r="D112">
+        <v>12.9</v>
+      </c>
+      <c r="E112">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B113" t="b">
+        <v>0</v>
+      </c>
+      <c r="C113" t="s">
+        <v>32</v>
+      </c>
+      <c r="D113">
+        <v>12.5</v>
+      </c>
+      <c r="E113">
+        <v>12.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EC696A-D114-477C-97A9-F988F8CF24A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64673782-540C-4DE4-A4A6-D862B3A25495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7155" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2318,6 +2318,446 @@
         <v>12.6</v>
       </c>
     </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B114" t="b">
+        <v>0</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E114">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B115" t="b">
+        <v>0</v>
+      </c>
+      <c r="C115" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115">
+        <v>13.4</v>
+      </c>
+      <c r="E115">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B116" t="b">
+        <v>0</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116">
+        <v>14.8</v>
+      </c>
+      <c r="E116">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B117" t="b">
+        <v>0</v>
+      </c>
+      <c r="C117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B118" t="b">
+        <v>0</v>
+      </c>
+      <c r="C118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B119" t="b">
+        <v>0</v>
+      </c>
+      <c r="C119" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B120" t="b">
+        <v>0</v>
+      </c>
+      <c r="C120" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120">
+        <v>16.3</v>
+      </c>
+      <c r="E120">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B121" t="b">
+        <v>0</v>
+      </c>
+      <c r="C121" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121">
+        <v>12.5</v>
+      </c>
+      <c r="E121">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B122" t="b">
+        <v>0</v>
+      </c>
+      <c r="C122" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122">
+        <v>14.9</v>
+      </c>
+      <c r="E122">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B123" t="b">
+        <v>0</v>
+      </c>
+      <c r="C123" t="s">
+        <v>14</v>
+      </c>
+      <c r="D123">
+        <v>12.8</v>
+      </c>
+      <c r="E123">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B124" t="b">
+        <v>0</v>
+      </c>
+      <c r="C124" t="s">
+        <v>15</v>
+      </c>
+      <c r="D124">
+        <v>12.1</v>
+      </c>
+      <c r="E124">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B125" t="b">
+        <v>0</v>
+      </c>
+      <c r="C125" t="s">
+        <v>16</v>
+      </c>
+      <c r="D125">
+        <v>14.4</v>
+      </c>
+      <c r="E125">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B126" t="b">
+        <v>0</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126">
+        <v>13.9</v>
+      </c>
+      <c r="E126">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B127" t="b">
+        <v>0</v>
+      </c>
+      <c r="C127" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127">
+        <v>13</v>
+      </c>
+      <c r="E127">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B128" t="b">
+        <v>0</v>
+      </c>
+      <c r="C128" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128">
+        <v>11.3</v>
+      </c>
+      <c r="E128">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B129" t="b">
+        <v>0</v>
+      </c>
+      <c r="C129" t="s">
+        <v>20</v>
+      </c>
+      <c r="D129">
+        <v>13.4</v>
+      </c>
+      <c r="E129">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B130" t="b">
+        <v>0</v>
+      </c>
+      <c r="C130" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B131" t="b">
+        <v>0</v>
+      </c>
+      <c r="C131" t="s">
+        <v>22</v>
+      </c>
+      <c r="D131">
+        <v>11.7</v>
+      </c>
+      <c r="E131">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="b">
+        <v>0</v>
+      </c>
+      <c r="C132" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B133" t="b">
+        <v>0</v>
+      </c>
+      <c r="C133" t="s">
+        <v>24</v>
+      </c>
+      <c r="D133">
+        <v>13.9</v>
+      </c>
+      <c r="E133">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B134" t="b">
+        <v>0</v>
+      </c>
+      <c r="C134" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B135" t="b">
+        <v>0</v>
+      </c>
+      <c r="C135" t="s">
+        <v>26</v>
+      </c>
+      <c r="D135">
+        <v>14.2</v>
+      </c>
+      <c r="E135">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B136" t="b">
+        <v>0</v>
+      </c>
+      <c r="C136" t="s">
+        <v>27</v>
+      </c>
+      <c r="D136">
+        <v>15.9</v>
+      </c>
+      <c r="E136">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B137" t="b">
+        <v>0</v>
+      </c>
+      <c r="C137" t="s">
+        <v>28</v>
+      </c>
+      <c r="D137">
+        <v>16.7</v>
+      </c>
+      <c r="E137">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B138" t="b">
+        <v>0</v>
+      </c>
+      <c r="C138" t="s">
+        <v>29</v>
+      </c>
+      <c r="D138">
+        <v>12.8</v>
+      </c>
+      <c r="E138">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B139" t="b">
+        <v>0</v>
+      </c>
+      <c r="C139" t="s">
+        <v>30</v>
+      </c>
+      <c r="D139">
+        <v>12.6</v>
+      </c>
+      <c r="E139">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B140" t="b">
+        <v>0</v>
+      </c>
+      <c r="C140" t="s">
+        <v>31</v>
+      </c>
+      <c r="D140">
+        <v>13.3</v>
+      </c>
+      <c r="E140">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B141" t="b">
+        <v>0</v>
+      </c>
+      <c r="C141" t="s">
+        <v>32</v>
+      </c>
+      <c r="D141">
+        <v>12.6</v>
+      </c>
+      <c r="E141">
+        <v>11.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64673782-540C-4DE4-A4A6-D862B3A25495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED69166C-495F-4616-8D28-2BB58BCB55EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7155" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="3630" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2758,6 +2758,452 @@
         <v>11.5</v>
       </c>
     </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B142" t="b">
+        <v>0</v>
+      </c>
+      <c r="C142" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142">
+        <v>15.2</v>
+      </c>
+      <c r="E142">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B143" t="b">
+        <v>0</v>
+      </c>
+      <c r="C143" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143">
+        <v>13.3</v>
+      </c>
+      <c r="E143">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B144" t="b">
+        <v>0</v>
+      </c>
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144">
+        <v>14.6</v>
+      </c>
+      <c r="E144">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B145" t="b">
+        <v>0</v>
+      </c>
+      <c r="C145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B146" t="b">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146">
+        <v>10.5</v>
+      </c>
+      <c r="E146">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B147" t="b">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B148" t="b">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
+        <v>11</v>
+      </c>
+      <c r="D148">
+        <v>14.9</v>
+      </c>
+      <c r="E148">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B149" t="b">
+        <v>0</v>
+      </c>
+      <c r="C149" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149">
+        <v>10.5</v>
+      </c>
+      <c r="E149">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B150" t="b">
+        <v>0</v>
+      </c>
+      <c r="C150" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150">
+        <v>13.6</v>
+      </c>
+      <c r="E150">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B151" t="b">
+        <v>0</v>
+      </c>
+      <c r="C151" t="s">
+        <v>14</v>
+      </c>
+      <c r="D151">
+        <v>12.7</v>
+      </c>
+      <c r="E151">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B152" t="b">
+        <v>0</v>
+      </c>
+      <c r="C152" t="s">
+        <v>15</v>
+      </c>
+      <c r="D152">
+        <v>13.5</v>
+      </c>
+      <c r="E152">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B153" t="b">
+        <v>0</v>
+      </c>
+      <c r="C153" t="s">
+        <v>16</v>
+      </c>
+      <c r="D153">
+        <v>13.9</v>
+      </c>
+      <c r="E153">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B154" t="b">
+        <v>0</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154">
+        <v>14.1</v>
+      </c>
+      <c r="E154">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B155" t="b">
+        <v>0</v>
+      </c>
+      <c r="C155" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155">
+        <v>14.4</v>
+      </c>
+      <c r="E155">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B156" t="b">
+        <v>0</v>
+      </c>
+      <c r="C156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156">
+        <v>11.2</v>
+      </c>
+      <c r="E156">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B157" t="b">
+        <v>0</v>
+      </c>
+      <c r="C157" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157">
+        <v>13.3</v>
+      </c>
+      <c r="E157">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B158" t="b">
+        <v>0</v>
+      </c>
+      <c r="C158" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B159" t="b">
+        <v>0</v>
+      </c>
+      <c r="C159" t="s">
+        <v>22</v>
+      </c>
+      <c r="D159">
+        <v>11.3</v>
+      </c>
+      <c r="E159">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B160" t="b">
+        <v>0</v>
+      </c>
+      <c r="C160" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B161" t="b">
+        <v>0</v>
+      </c>
+      <c r="C161" t="s">
+        <v>24</v>
+      </c>
+      <c r="D161">
+        <v>13.7</v>
+      </c>
+      <c r="E161">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B162" t="b">
+        <v>0</v>
+      </c>
+      <c r="C162" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B163" t="b">
+        <v>0</v>
+      </c>
+      <c r="C163" t="s">
+        <v>26</v>
+      </c>
+      <c r="D163">
+        <v>13.7</v>
+      </c>
+      <c r="E163">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B164" t="b">
+        <v>0</v>
+      </c>
+      <c r="C164" t="s">
+        <v>27</v>
+      </c>
+      <c r="D164">
+        <v>14.7</v>
+      </c>
+      <c r="E164">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B165" t="b">
+        <v>0</v>
+      </c>
+      <c r="C165" t="s">
+        <v>28</v>
+      </c>
+      <c r="D165">
+        <v>15</v>
+      </c>
+      <c r="E165">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B166" t="b">
+        <v>0</v>
+      </c>
+      <c r="C166" t="s">
+        <v>29</v>
+      </c>
+      <c r="D166">
+        <v>12.1</v>
+      </c>
+      <c r="E166">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B167" t="b">
+        <v>0</v>
+      </c>
+      <c r="C167" t="s">
+        <v>30</v>
+      </c>
+      <c r="D167">
+        <v>13.4</v>
+      </c>
+      <c r="E167">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B168" t="b">
+        <v>0</v>
+      </c>
+      <c r="C168" t="s">
+        <v>31</v>
+      </c>
+      <c r="D168">
+        <v>13.2</v>
+      </c>
+      <c r="E168">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B169" t="b">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s">
+        <v>32</v>
+      </c>
+      <c r="D169">
+        <v>12.4</v>
+      </c>
+      <c r="E169">
+        <v>12.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED69166C-495F-4616-8D28-2BB58BCB55EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F7E51C-F302-438A-9FE2-4187786A29AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="3630" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -3204,6 +3204,928 @@
         <v>12.1</v>
       </c>
     </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B170" t="b">
+        <v>1</v>
+      </c>
+      <c r="C170" t="s">
+        <v>5</v>
+      </c>
+      <c r="D170">
+        <v>17.7</v>
+      </c>
+      <c r="E170">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B171" t="b">
+        <v>1</v>
+      </c>
+      <c r="C171" t="s">
+        <v>6</v>
+      </c>
+      <c r="D171">
+        <v>14.4</v>
+      </c>
+      <c r="E171">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B172" t="b">
+        <v>1</v>
+      </c>
+      <c r="C172" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172">
+        <v>15.4</v>
+      </c>
+      <c r="E172">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B173" t="b">
+        <v>1</v>
+      </c>
+      <c r="C173" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173">
+        <v>14.6</v>
+      </c>
+      <c r="E173">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B174" t="b">
+        <v>1</v>
+      </c>
+      <c r="C174" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174">
+        <v>12.3</v>
+      </c>
+      <c r="E174">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B175" t="b">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B176" t="b">
+        <v>1</v>
+      </c>
+      <c r="C176" t="s">
+        <v>11</v>
+      </c>
+      <c r="D176">
+        <v>16</v>
+      </c>
+      <c r="E176">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B177" t="b">
+        <v>1</v>
+      </c>
+      <c r="C177" t="s">
+        <v>12</v>
+      </c>
+      <c r="D177">
+        <v>11.2</v>
+      </c>
+      <c r="E177">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B178" t="b">
+        <v>1</v>
+      </c>
+      <c r="C178" t="s">
+        <v>13</v>
+      </c>
+      <c r="D178">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E178">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B179" t="b">
+        <v>1</v>
+      </c>
+      <c r="C179" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179">
+        <v>13.7</v>
+      </c>
+      <c r="E179">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B180" t="b">
+        <v>1</v>
+      </c>
+      <c r="C180" t="s">
+        <v>15</v>
+      </c>
+      <c r="D180">
+        <v>13.2</v>
+      </c>
+      <c r="E180">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B181" t="b">
+        <v>1</v>
+      </c>
+      <c r="C181" t="s">
+        <v>16</v>
+      </c>
+      <c r="D181">
+        <v>13.9</v>
+      </c>
+      <c r="E181">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B182" t="b">
+        <v>1</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182">
+        <v>14.8</v>
+      </c>
+      <c r="E182">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B183" t="b">
+        <v>1</v>
+      </c>
+      <c r="C183" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183">
+        <v>15.8</v>
+      </c>
+      <c r="E183">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B184" t="b">
+        <v>1</v>
+      </c>
+      <c r="C184" t="s">
+        <v>19</v>
+      </c>
+      <c r="D184">
+        <v>12.4</v>
+      </c>
+      <c r="E184">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B185" t="b">
+        <v>1</v>
+      </c>
+      <c r="C185" t="s">
+        <v>20</v>
+      </c>
+      <c r="D185">
+        <v>13.4</v>
+      </c>
+      <c r="E185">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B186" t="b">
+        <v>1</v>
+      </c>
+      <c r="C186" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186">
+        <v>16.2</v>
+      </c>
+      <c r="E186">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B187" t="b">
+        <v>1</v>
+      </c>
+      <c r="C187" t="s">
+        <v>22</v>
+      </c>
+      <c r="D187">
+        <v>11.6</v>
+      </c>
+      <c r="E187">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B188" t="b">
+        <v>1</v>
+      </c>
+      <c r="C188" t="s">
+        <v>23</v>
+      </c>
+      <c r="D188">
+        <v>14.3</v>
+      </c>
+      <c r="E188">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B189" t="b">
+        <v>1</v>
+      </c>
+      <c r="C189" t="s">
+        <v>24</v>
+      </c>
+      <c r="D189">
+        <v>15.1</v>
+      </c>
+      <c r="E189">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B190" t="b">
+        <v>1</v>
+      </c>
+      <c r="C190" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B191" t="b">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s">
+        <v>26</v>
+      </c>
+      <c r="D191">
+        <v>14.1</v>
+      </c>
+      <c r="E191">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B192" t="b">
+        <v>1</v>
+      </c>
+      <c r="C192" t="s">
+        <v>27</v>
+      </c>
+      <c r="D192">
+        <v>17.3</v>
+      </c>
+      <c r="E192">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B193" t="b">
+        <v>1</v>
+      </c>
+      <c r="C193" t="s">
+        <v>28</v>
+      </c>
+      <c r="D193">
+        <v>17.7</v>
+      </c>
+      <c r="E193">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B194" t="b">
+        <v>1</v>
+      </c>
+      <c r="C194" t="s">
+        <v>29</v>
+      </c>
+      <c r="D194">
+        <v>13.9</v>
+      </c>
+      <c r="E194">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B195" t="b">
+        <v>1</v>
+      </c>
+      <c r="C195" t="s">
+        <v>30</v>
+      </c>
+      <c r="D195">
+        <v>13.3</v>
+      </c>
+      <c r="E195">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B196" t="b">
+        <v>1</v>
+      </c>
+      <c r="C196" t="s">
+        <v>31</v>
+      </c>
+      <c r="D196">
+        <v>12.8</v>
+      </c>
+      <c r="E196">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B197" t="b">
+        <v>1</v>
+      </c>
+      <c r="C197" t="s">
+        <v>32</v>
+      </c>
+      <c r="D197">
+        <v>12.3</v>
+      </c>
+      <c r="E197">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B198" t="b">
+        <v>0</v>
+      </c>
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+      <c r="D198">
+        <v>14.9</v>
+      </c>
+      <c r="E198">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B199" t="b">
+        <v>0</v>
+      </c>
+      <c r="C199" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199">
+        <v>13.9</v>
+      </c>
+      <c r="E199">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B200" t="b">
+        <v>0</v>
+      </c>
+      <c r="C200" t="s">
+        <v>7</v>
+      </c>
+      <c r="D200">
+        <v>14.1</v>
+      </c>
+      <c r="E200">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B201" t="b">
+        <v>0</v>
+      </c>
+      <c r="C201" t="s">
+        <v>8</v>
+      </c>
+      <c r="D201">
+        <v>14.7</v>
+      </c>
+      <c r="E201">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B202" t="b">
+        <v>0</v>
+      </c>
+      <c r="C202" t="s">
+        <v>9</v>
+      </c>
+      <c r="D202">
+        <v>11.8</v>
+      </c>
+      <c r="E202">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B203" t="b">
+        <v>0</v>
+      </c>
+      <c r="C203" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B204" t="b">
+        <v>0</v>
+      </c>
+      <c r="C204" t="s">
+        <v>11</v>
+      </c>
+      <c r="D204">
+        <v>15.4</v>
+      </c>
+      <c r="E204">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B205" t="b">
+        <v>0</v>
+      </c>
+      <c r="C205" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205">
+        <v>10.3</v>
+      </c>
+      <c r="E205">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B206" t="b">
+        <v>0</v>
+      </c>
+      <c r="C206" t="s">
+        <v>13</v>
+      </c>
+      <c r="D206">
+        <v>13.8</v>
+      </c>
+      <c r="E206">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B207" t="b">
+        <v>0</v>
+      </c>
+      <c r="C207" t="s">
+        <v>14</v>
+      </c>
+      <c r="D207">
+        <v>12.9</v>
+      </c>
+      <c r="E207">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B208" t="b">
+        <v>0</v>
+      </c>
+      <c r="C208" t="s">
+        <v>15</v>
+      </c>
+      <c r="D208">
+        <v>13.2</v>
+      </c>
+      <c r="E208">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B209" t="b">
+        <v>0</v>
+      </c>
+      <c r="C209" t="s">
+        <v>16</v>
+      </c>
+      <c r="D209">
+        <v>14.3</v>
+      </c>
+      <c r="E209">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B210" t="b">
+        <v>0</v>
+      </c>
+      <c r="C210" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210">
+        <v>13.2</v>
+      </c>
+      <c r="E210">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B211" t="b">
+        <v>0</v>
+      </c>
+      <c r="C211" t="s">
+        <v>18</v>
+      </c>
+      <c r="D211">
+        <v>14.5</v>
+      </c>
+      <c r="E211">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B212" t="b">
+        <v>0</v>
+      </c>
+      <c r="C212" t="s">
+        <v>19</v>
+      </c>
+      <c r="D212">
+        <v>11.5</v>
+      </c>
+      <c r="E212">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B213" t="b">
+        <v>0</v>
+      </c>
+      <c r="C213" t="s">
+        <v>20</v>
+      </c>
+      <c r="D213">
+        <v>12.7</v>
+      </c>
+      <c r="E213">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B214" t="b">
+        <v>0</v>
+      </c>
+      <c r="C214" t="s">
+        <v>21</v>
+      </c>
+      <c r="D214">
+        <v>15.8</v>
+      </c>
+      <c r="E214">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B215" t="b">
+        <v>0</v>
+      </c>
+      <c r="C215" t="s">
+        <v>22</v>
+      </c>
+      <c r="D215">
+        <v>11.2</v>
+      </c>
+      <c r="E215">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B216" t="b">
+        <v>0</v>
+      </c>
+      <c r="C216" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B217" t="b">
+        <v>0</v>
+      </c>
+      <c r="C217" t="s">
+        <v>24</v>
+      </c>
+      <c r="D217">
+        <v>13.3</v>
+      </c>
+      <c r="E217">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B218" t="b">
+        <v>0</v>
+      </c>
+      <c r="C218" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B219" t="b">
+        <v>0</v>
+      </c>
+      <c r="C219" t="s">
+        <v>26</v>
+      </c>
+      <c r="D219">
+        <v>14.9</v>
+      </c>
+      <c r="E219">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B220" t="b">
+        <v>0</v>
+      </c>
+      <c r="C220" t="s">
+        <v>27</v>
+      </c>
+      <c r="D220">
+        <v>13.9</v>
+      </c>
+      <c r="E220">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B221" t="b">
+        <v>0</v>
+      </c>
+      <c r="C221" t="s">
+        <v>28</v>
+      </c>
+      <c r="D221">
+        <v>14.8</v>
+      </c>
+      <c r="E221">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B222" t="b">
+        <v>0</v>
+      </c>
+      <c r="C222" t="s">
+        <v>29</v>
+      </c>
+      <c r="D222">
+        <v>13.4</v>
+      </c>
+      <c r="E222">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B223" t="b">
+        <v>0</v>
+      </c>
+      <c r="C223" t="s">
+        <v>30</v>
+      </c>
+      <c r="D223">
+        <v>13.4</v>
+      </c>
+      <c r="E223">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B224" t="b">
+        <v>0</v>
+      </c>
+      <c r="C224" t="s">
+        <v>31</v>
+      </c>
+      <c r="D224">
+        <v>12.1</v>
+      </c>
+      <c r="E224">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B225" t="b">
+        <v>0</v>
+      </c>
+      <c r="C225" t="s">
+        <v>32</v>
+      </c>
+      <c r="D225">
+        <v>12.7</v>
+      </c>
+      <c r="E225">
+        <v>12.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F7E51C-F302-438A-9FE2-4187786A29AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7A5D79-6074-424D-B265-990C7680695E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1770" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -4126,6 +4126,476 @@
         <v>12.2</v>
       </c>
     </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B226" t="b">
+        <v>0</v>
+      </c>
+      <c r="C226" t="s">
+        <v>5</v>
+      </c>
+      <c r="D226">
+        <v>14.4</v>
+      </c>
+      <c r="E226">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B227" t="b">
+        <v>0</v>
+      </c>
+      <c r="C227" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227">
+        <v>12.8</v>
+      </c>
+      <c r="E227">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B228" t="b">
+        <v>0</v>
+      </c>
+      <c r="C228" t="s">
+        <v>7</v>
+      </c>
+      <c r="D228">
+        <v>14.2</v>
+      </c>
+      <c r="E228">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B229" t="b">
+        <v>0</v>
+      </c>
+      <c r="C229" t="s">
+        <v>8</v>
+      </c>
+      <c r="D229">
+        <v>13.9</v>
+      </c>
+      <c r="E229">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B230" t="b">
+        <v>0</v>
+      </c>
+      <c r="C230" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230">
+        <v>10.7</v>
+      </c>
+      <c r="E230">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B231" t="b">
+        <v>0</v>
+      </c>
+      <c r="C231" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B232" t="b">
+        <v>0</v>
+      </c>
+      <c r="C232" t="s">
+        <v>11</v>
+      </c>
+      <c r="D232">
+        <v>15.3</v>
+      </c>
+      <c r="E232">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B233" t="b">
+        <v>0</v>
+      </c>
+      <c r="C233" t="s">
+        <v>12</v>
+      </c>
+      <c r="D233">
+        <v>10.7</v>
+      </c>
+      <c r="E233">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B234" t="b">
+        <v>0</v>
+      </c>
+      <c r="C234" t="s">
+        <v>13</v>
+      </c>
+      <c r="D234">
+        <v>13.2</v>
+      </c>
+      <c r="E234">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B235" t="b">
+        <v>0</v>
+      </c>
+      <c r="C235" t="s">
+        <v>14</v>
+      </c>
+      <c r="D235">
+        <v>12.7</v>
+      </c>
+      <c r="E235">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B236" t="b">
+        <v>0</v>
+      </c>
+      <c r="C236" t="s">
+        <v>15</v>
+      </c>
+      <c r="D236">
+        <v>13.5</v>
+      </c>
+      <c r="E236">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B237" t="b">
+        <v>0</v>
+      </c>
+      <c r="C237" t="s">
+        <v>16</v>
+      </c>
+      <c r="D237">
+        <v>13.4</v>
+      </c>
+      <c r="E237">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B238" t="b">
+        <v>0</v>
+      </c>
+      <c r="C238" t="s">
+        <v>17</v>
+      </c>
+      <c r="D238">
+        <v>12.4</v>
+      </c>
+      <c r="E238">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B239" t="b">
+        <v>0</v>
+      </c>
+      <c r="C239" t="s">
+        <v>18</v>
+      </c>
+      <c r="D239">
+        <v>14</v>
+      </c>
+      <c r="E239">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B240" t="b">
+        <v>0</v>
+      </c>
+      <c r="C240" t="s">
+        <v>19</v>
+      </c>
+      <c r="D240">
+        <v>11.1</v>
+      </c>
+      <c r="E240">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B241" t="b">
+        <v>0</v>
+      </c>
+      <c r="C241" t="s">
+        <v>20</v>
+      </c>
+      <c r="D241">
+        <v>12.4</v>
+      </c>
+      <c r="E241">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B242" t="b">
+        <v>0</v>
+      </c>
+      <c r="C242" t="s">
+        <v>21</v>
+      </c>
+      <c r="D242">
+        <v>15.5</v>
+      </c>
+      <c r="E242">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B243" t="b">
+        <v>0</v>
+      </c>
+      <c r="C243" t="s">
+        <v>22</v>
+      </c>
+      <c r="D243">
+        <v>10.8</v>
+      </c>
+      <c r="E243">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B244" t="b">
+        <v>0</v>
+      </c>
+      <c r="C244" t="s">
+        <v>23</v>
+      </c>
+      <c r="D244">
+        <v>15.2</v>
+      </c>
+      <c r="E244">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B245" t="b">
+        <v>0</v>
+      </c>
+      <c r="C245" t="s">
+        <v>24</v>
+      </c>
+      <c r="D245">
+        <v>13.5</v>
+      </c>
+      <c r="E245">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B246" t="b">
+        <v>0</v>
+      </c>
+      <c r="C246" t="s">
+        <v>25</v>
+      </c>
+      <c r="D246">
+        <v>9.6</v>
+      </c>
+      <c r="E246">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B247" t="b">
+        <v>0</v>
+      </c>
+      <c r="C247" t="s">
+        <v>26</v>
+      </c>
+      <c r="D247">
+        <v>13.4</v>
+      </c>
+      <c r="E247">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B248" t="b">
+        <v>0</v>
+      </c>
+      <c r="C248" t="s">
+        <v>27</v>
+      </c>
+      <c r="D248">
+        <v>16.2</v>
+      </c>
+      <c r="E248">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B249" t="b">
+        <v>0</v>
+      </c>
+      <c r="C249" t="s">
+        <v>28</v>
+      </c>
+      <c r="D249">
+        <v>15.7</v>
+      </c>
+      <c r="E249">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B250" t="b">
+        <v>0</v>
+      </c>
+      <c r="C250" t="s">
+        <v>29</v>
+      </c>
+      <c r="D250">
+        <v>11.7</v>
+      </c>
+      <c r="E250">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B251" t="b">
+        <v>0</v>
+      </c>
+      <c r="C251" t="s">
+        <v>30</v>
+      </c>
+      <c r="D251">
+        <v>13</v>
+      </c>
+      <c r="E251">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B252" t="b">
+        <v>0</v>
+      </c>
+      <c r="C252" t="s">
+        <v>31</v>
+      </c>
+      <c r="D252">
+        <v>13.4</v>
+      </c>
+      <c r="E252">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B253" t="b">
+        <v>0</v>
+      </c>
+      <c r="C253" t="s">
+        <v>32</v>
+      </c>
+      <c r="D253">
+        <v>11.9</v>
+      </c>
+      <c r="E253">
+        <v>11.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7A5D79-6074-424D-B265-990C7680695E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A234CB-3017-4C32-BC00-18EA622856BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -4596,6 +4596,464 @@
         <v>11.7</v>
       </c>
     </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B254" t="b">
+        <v>0</v>
+      </c>
+      <c r="C254" t="s">
+        <v>5</v>
+      </c>
+      <c r="D254">
+        <v>14.2</v>
+      </c>
+      <c r="E254">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B255" t="b">
+        <v>0</v>
+      </c>
+      <c r="C255" t="s">
+        <v>6</v>
+      </c>
+      <c r="D255">
+        <v>13.9</v>
+      </c>
+      <c r="E255">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B256" t="b">
+        <v>0</v>
+      </c>
+      <c r="C256" t="s">
+        <v>7</v>
+      </c>
+      <c r="D256">
+        <v>13.9</v>
+      </c>
+      <c r="E256">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B257" t="b">
+        <v>0</v>
+      </c>
+      <c r="C257" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B258" t="b">
+        <v>0</v>
+      </c>
+      <c r="C258" t="s">
+        <v>9</v>
+      </c>
+      <c r="D258">
+        <v>11.3</v>
+      </c>
+      <c r="E258">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B259" t="b">
+        <v>0</v>
+      </c>
+      <c r="C259" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B260" t="b">
+        <v>0</v>
+      </c>
+      <c r="C260" t="s">
+        <v>11</v>
+      </c>
+      <c r="D260">
+        <v>15.1</v>
+      </c>
+      <c r="E260">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B261" t="b">
+        <v>0</v>
+      </c>
+      <c r="C261" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261">
+        <v>10.3</v>
+      </c>
+      <c r="E261">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B262" t="b">
+        <v>0</v>
+      </c>
+      <c r="C262" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B263" t="b">
+        <v>0</v>
+      </c>
+      <c r="C263" t="s">
+        <v>14</v>
+      </c>
+      <c r="D263">
+        <v>13.2</v>
+      </c>
+      <c r="E263">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B264" t="b">
+        <v>0</v>
+      </c>
+      <c r="C264" t="s">
+        <v>15</v>
+      </c>
+      <c r="D264">
+        <v>13.8</v>
+      </c>
+      <c r="E264">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B265" t="b">
+        <v>0</v>
+      </c>
+      <c r="C265" t="s">
+        <v>16</v>
+      </c>
+      <c r="D265">
+        <v>13.8</v>
+      </c>
+      <c r="E265">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B266" t="b">
+        <v>0</v>
+      </c>
+      <c r="C266" t="s">
+        <v>17</v>
+      </c>
+      <c r="D266">
+        <v>13.3</v>
+      </c>
+      <c r="E266">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B267" t="b">
+        <v>0</v>
+      </c>
+      <c r="C267" t="s">
+        <v>18</v>
+      </c>
+      <c r="D267">
+        <v>14</v>
+      </c>
+      <c r="E267">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B268" t="b">
+        <v>0</v>
+      </c>
+      <c r="C268" t="s">
+        <v>19</v>
+      </c>
+      <c r="D268">
+        <v>10.9</v>
+      </c>
+      <c r="E268">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B269" t="b">
+        <v>0</v>
+      </c>
+      <c r="C269" t="s">
+        <v>20</v>
+      </c>
+      <c r="D269">
+        <v>13</v>
+      </c>
+      <c r="E269">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B270" t="b">
+        <v>0</v>
+      </c>
+      <c r="C270" t="s">
+        <v>21</v>
+      </c>
+      <c r="D270">
+        <v>15.4</v>
+      </c>
+      <c r="E270">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B271" t="b">
+        <v>0</v>
+      </c>
+      <c r="C271" t="s">
+        <v>22</v>
+      </c>
+      <c r="D271">
+        <v>11.2</v>
+      </c>
+      <c r="E271">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B272" t="b">
+        <v>0</v>
+      </c>
+      <c r="C272" t="s">
+        <v>23</v>
+      </c>
+      <c r="D272">
+        <v>14.5</v>
+      </c>
+      <c r="E272">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B273" t="b">
+        <v>0</v>
+      </c>
+      <c r="C273" t="s">
+        <v>24</v>
+      </c>
+      <c r="D273">
+        <v>13.9</v>
+      </c>
+      <c r="E273">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B274" t="b">
+        <v>0</v>
+      </c>
+      <c r="C274" t="s">
+        <v>25</v>
+      </c>
+      <c r="D274">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E274">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B275" t="b">
+        <v>0</v>
+      </c>
+      <c r="C275" t="s">
+        <v>26</v>
+      </c>
+      <c r="D275">
+        <v>13.4</v>
+      </c>
+      <c r="E275">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B276" t="b">
+        <v>0</v>
+      </c>
+      <c r="C276" t="s">
+        <v>27</v>
+      </c>
+      <c r="D276">
+        <v>15.4</v>
+      </c>
+      <c r="E276">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B277" t="b">
+        <v>0</v>
+      </c>
+      <c r="C277" t="s">
+        <v>28</v>
+      </c>
+      <c r="D277">
+        <v>16</v>
+      </c>
+      <c r="E277">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B278" t="b">
+        <v>0</v>
+      </c>
+      <c r="C278" t="s">
+        <v>29</v>
+      </c>
+      <c r="D278">
+        <v>13.6</v>
+      </c>
+      <c r="E278">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B279" t="b">
+        <v>0</v>
+      </c>
+      <c r="C279" t="s">
+        <v>30</v>
+      </c>
+      <c r="D279">
+        <v>12.4</v>
+      </c>
+      <c r="E279">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B280" t="b">
+        <v>0</v>
+      </c>
+      <c r="C280" t="s">
+        <v>31</v>
+      </c>
+      <c r="D280">
+        <v>13</v>
+      </c>
+      <c r="E280">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B281" t="b">
+        <v>0</v>
+      </c>
+      <c r="C281" t="s">
+        <v>32</v>
+      </c>
+      <c r="D281">
+        <v>11.6</v>
+      </c>
+      <c r="E281">
+        <v>10.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A234CB-3017-4C32-BC00-18EA622856BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A603B48E-4C47-483E-8870-4BAC88E821F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E309"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -5054,6 +5054,464 @@
         <v>10.5</v>
       </c>
     </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B282" t="b">
+        <v>0</v>
+      </c>
+      <c r="C282" t="s">
+        <v>5</v>
+      </c>
+      <c r="D282">
+        <v>14.7</v>
+      </c>
+      <c r="E282">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B283" t="b">
+        <v>0</v>
+      </c>
+      <c r="C283" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283">
+        <v>13.5</v>
+      </c>
+      <c r="E283">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B284" t="b">
+        <v>0</v>
+      </c>
+      <c r="C284" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B285" t="b">
+        <v>0</v>
+      </c>
+      <c r="C285" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285">
+        <v>13.7</v>
+      </c>
+      <c r="E285">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B286" t="b">
+        <v>0</v>
+      </c>
+      <c r="C286" t="s">
+        <v>9</v>
+      </c>
+      <c r="D286">
+        <v>12.5</v>
+      </c>
+      <c r="E286">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B287" t="b">
+        <v>0</v>
+      </c>
+      <c r="C287" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B288" t="b">
+        <v>0</v>
+      </c>
+      <c r="C288" t="s">
+        <v>11</v>
+      </c>
+      <c r="D288">
+        <v>15.5</v>
+      </c>
+      <c r="E288">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B289" t="b">
+        <v>0</v>
+      </c>
+      <c r="C289" t="s">
+        <v>12</v>
+      </c>
+      <c r="D289">
+        <v>9.9</v>
+      </c>
+      <c r="E289">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B290" t="b">
+        <v>0</v>
+      </c>
+      <c r="C290" t="s">
+        <v>13</v>
+      </c>
+      <c r="D290">
+        <v>14.7</v>
+      </c>
+      <c r="E290">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B291" t="b">
+        <v>0</v>
+      </c>
+      <c r="C291" t="s">
+        <v>14</v>
+      </c>
+      <c r="D291">
+        <v>13.5</v>
+      </c>
+      <c r="E291">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B292" t="b">
+        <v>0</v>
+      </c>
+      <c r="C292" t="s">
+        <v>15</v>
+      </c>
+      <c r="D292">
+        <v>13.6</v>
+      </c>
+      <c r="E292">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B293" t="b">
+        <v>0</v>
+      </c>
+      <c r="C293" t="s">
+        <v>16</v>
+      </c>
+      <c r="D293">
+        <v>13.8</v>
+      </c>
+      <c r="E293">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B294" t="b">
+        <v>0</v>
+      </c>
+      <c r="C294" t="s">
+        <v>17</v>
+      </c>
+      <c r="D294">
+        <v>13.9</v>
+      </c>
+      <c r="E294">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B295" t="b">
+        <v>0</v>
+      </c>
+      <c r="C295" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B296" t="b">
+        <v>0</v>
+      </c>
+      <c r="C296" t="s">
+        <v>19</v>
+      </c>
+      <c r="D296">
+        <v>12.2</v>
+      </c>
+      <c r="E296">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B297" t="b">
+        <v>0</v>
+      </c>
+      <c r="C297" t="s">
+        <v>20</v>
+      </c>
+      <c r="D297">
+        <v>12.7</v>
+      </c>
+      <c r="E297">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B298" t="b">
+        <v>0</v>
+      </c>
+      <c r="C298" t="s">
+        <v>21</v>
+      </c>
+      <c r="D298">
+        <v>15.4</v>
+      </c>
+      <c r="E298">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B299" t="b">
+        <v>0</v>
+      </c>
+      <c r="C299" t="s">
+        <v>22</v>
+      </c>
+      <c r="D299">
+        <v>10.9</v>
+      </c>
+      <c r="E299">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B300" t="b">
+        <v>0</v>
+      </c>
+      <c r="C300" t="s">
+        <v>23</v>
+      </c>
+      <c r="D300">
+        <v>15.7</v>
+      </c>
+      <c r="E300">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B301" t="b">
+        <v>0</v>
+      </c>
+      <c r="C301" t="s">
+        <v>24</v>
+      </c>
+      <c r="D301">
+        <v>13.5</v>
+      </c>
+      <c r="E301">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B302" t="b">
+        <v>0</v>
+      </c>
+      <c r="C302" t="s">
+        <v>25</v>
+      </c>
+      <c r="D302">
+        <v>9.5</v>
+      </c>
+      <c r="E302">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B303" t="b">
+        <v>0</v>
+      </c>
+      <c r="C303" t="s">
+        <v>26</v>
+      </c>
+      <c r="D303">
+        <v>13.2</v>
+      </c>
+      <c r="E303">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B304" t="b">
+        <v>0</v>
+      </c>
+      <c r="C304" t="s">
+        <v>27</v>
+      </c>
+      <c r="D304">
+        <v>15.2</v>
+      </c>
+      <c r="E304">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B305" t="b">
+        <v>0</v>
+      </c>
+      <c r="C305" t="s">
+        <v>28</v>
+      </c>
+      <c r="D305">
+        <v>15.7</v>
+      </c>
+      <c r="E305">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A306" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B306" t="b">
+        <v>0</v>
+      </c>
+      <c r="C306" t="s">
+        <v>29</v>
+      </c>
+      <c r="D306">
+        <v>13.7</v>
+      </c>
+      <c r="E306">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A307" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B307" t="b">
+        <v>0</v>
+      </c>
+      <c r="C307" t="s">
+        <v>30</v>
+      </c>
+      <c r="D307">
+        <v>13</v>
+      </c>
+      <c r="E307">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A308" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B308" t="b">
+        <v>0</v>
+      </c>
+      <c r="C308" t="s">
+        <v>31</v>
+      </c>
+      <c r="D308">
+        <v>12.8</v>
+      </c>
+      <c r="E308">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B309" t="b">
+        <v>0</v>
+      </c>
+      <c r="C309" t="s">
+        <v>32</v>
+      </c>
+      <c r="D309">
+        <v>12.4</v>
+      </c>
+      <c r="E309">
+        <v>11.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A603B48E-4C47-483E-8870-4BAC88E821F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162F6524-D0E2-4F23-B3FC-672667CE67ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E309"/>
+  <dimension ref="A1:E337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -5512,6 +5512,422 @@
         <v>11.6</v>
       </c>
     </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B310" t="b">
+        <v>1</v>
+      </c>
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E310">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B311" t="b">
+        <v>1</v>
+      </c>
+      <c r="C311" t="s">
+        <v>6</v>
+      </c>
+      <c r="D311">
+        <v>13.3</v>
+      </c>
+      <c r="E311">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B312" t="b">
+        <v>1</v>
+      </c>
+      <c r="C312" t="s">
+        <v>7</v>
+      </c>
+      <c r="D312">
+        <v>14.8</v>
+      </c>
+      <c r="E312">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B313" t="b">
+        <v>1</v>
+      </c>
+      <c r="C313" t="s">
+        <v>8</v>
+      </c>
+      <c r="D313">
+        <v>13.7</v>
+      </c>
+      <c r="E313">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B314" t="b">
+        <v>1</v>
+      </c>
+      <c r="C314" t="s">
+        <v>9</v>
+      </c>
+      <c r="D314">
+        <v>11.2</v>
+      </c>
+      <c r="E314">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A315" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B315" t="b">
+        <v>1</v>
+      </c>
+      <c r="C315" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A316" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B316" t="b">
+        <v>1</v>
+      </c>
+      <c r="C316" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A317" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B317" t="b">
+        <v>1</v>
+      </c>
+      <c r="C317" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A318" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B318" t="b">
+        <v>1</v>
+      </c>
+      <c r="C318" t="s">
+        <v>13</v>
+      </c>
+      <c r="D318">
+        <v>14.9</v>
+      </c>
+      <c r="E318">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A319" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B319" t="b">
+        <v>1</v>
+      </c>
+      <c r="C319" t="s">
+        <v>14</v>
+      </c>
+      <c r="D319">
+        <v>12.8</v>
+      </c>
+      <c r="E319">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B320" t="b">
+        <v>1</v>
+      </c>
+      <c r="C320" t="s">
+        <v>15</v>
+      </c>
+      <c r="D320">
+        <v>13.3</v>
+      </c>
+      <c r="E320">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B321" t="b">
+        <v>1</v>
+      </c>
+      <c r="C321" t="s">
+        <v>16</v>
+      </c>
+      <c r="D321">
+        <v>14</v>
+      </c>
+      <c r="E321">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B322" t="b">
+        <v>1</v>
+      </c>
+      <c r="C322" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B323" t="b">
+        <v>1</v>
+      </c>
+      <c r="C323" t="s">
+        <v>18</v>
+      </c>
+      <c r="D323">
+        <v>14.6</v>
+      </c>
+      <c r="E323">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B324" t="b">
+        <v>1</v>
+      </c>
+      <c r="C324" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B325" t="b">
+        <v>1</v>
+      </c>
+      <c r="C325" t="s">
+        <v>20</v>
+      </c>
+      <c r="D325">
+        <v>13.3</v>
+      </c>
+      <c r="E325">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B326" t="b">
+        <v>1</v>
+      </c>
+      <c r="C326" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B327" t="b">
+        <v>1</v>
+      </c>
+      <c r="C327" t="s">
+        <v>22</v>
+      </c>
+      <c r="D327">
+        <v>10.8</v>
+      </c>
+      <c r="E327">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B328" t="b">
+        <v>1</v>
+      </c>
+      <c r="C328" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B329" t="b">
+        <v>1</v>
+      </c>
+      <c r="C329" t="s">
+        <v>24</v>
+      </c>
+      <c r="D329">
+        <v>13.8</v>
+      </c>
+      <c r="E329">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B330" t="b">
+        <v>1</v>
+      </c>
+      <c r="C330" t="s">
+        <v>25</v>
+      </c>
+      <c r="D330">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E330">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B331" t="b">
+        <v>1</v>
+      </c>
+      <c r="C331" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B332" t="b">
+        <v>1</v>
+      </c>
+      <c r="C332" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A333" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B333" t="b">
+        <v>1</v>
+      </c>
+      <c r="C333" t="s">
+        <v>28</v>
+      </c>
+      <c r="D333">
+        <v>17.3</v>
+      </c>
+      <c r="E333">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A334" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B334" t="b">
+        <v>1</v>
+      </c>
+      <c r="C334" t="s">
+        <v>29</v>
+      </c>
+      <c r="D334">
+        <v>13.9</v>
+      </c>
+      <c r="E334">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A335" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B335" t="b">
+        <v>1</v>
+      </c>
+      <c r="C335" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A336" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B336" t="b">
+        <v>1</v>
+      </c>
+      <c r="C336" t="s">
+        <v>31</v>
+      </c>
+      <c r="D336">
+        <v>12.1</v>
+      </c>
+      <c r="E336">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B337" t="b">
+        <v>1</v>
+      </c>
+      <c r="C337" t="s">
+        <v>32</v>
+      </c>
+      <c r="D337">
+        <v>11.3</v>
+      </c>
+      <c r="E337">
+        <v>11.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/WSOC_CMJ_Season.xlsx
+++ b/sample_data/WSOC_CMJ_Season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahc\Desktop\PLNU_WSOC_SS\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162F6524-D0E2-4F23-B3FC-672667CE67ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7FA206-7A41-4CF9-87FA-A96BC6CA3041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="1440" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E337"/>
+  <dimension ref="A1:E365"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -5928,6 +5928,470 @@
         <v>11.7</v>
       </c>
     </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B338" t="b">
+        <v>0</v>
+      </c>
+      <c r="C338" t="s">
+        <v>5</v>
+      </c>
+      <c r="D338">
+        <v>13.8</v>
+      </c>
+      <c r="E338">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A339" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B339" t="b">
+        <v>0</v>
+      </c>
+      <c r="C339" t="s">
+        <v>6</v>
+      </c>
+      <c r="D339">
+        <v>14.3</v>
+      </c>
+      <c r="E339">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A340" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B340" t="b">
+        <v>0</v>
+      </c>
+      <c r="C340" t="s">
+        <v>7</v>
+      </c>
+      <c r="D340">
+        <v>15.4</v>
+      </c>
+      <c r="E340">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A341" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B341" t="b">
+        <v>0</v>
+      </c>
+      <c r="C341" t="s">
+        <v>8</v>
+      </c>
+      <c r="D341">
+        <v>13.8</v>
+      </c>
+      <c r="E341">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A342" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B342" t="b">
+        <v>0</v>
+      </c>
+      <c r="C342" t="s">
+        <v>9</v>
+      </c>
+      <c r="D342">
+        <v>11.7</v>
+      </c>
+      <c r="E342">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A343" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B343" t="b">
+        <v>0</v>
+      </c>
+      <c r="C343" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A344" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B344" t="b">
+        <v>0</v>
+      </c>
+      <c r="C344" t="s">
+        <v>11</v>
+      </c>
+      <c r="D344">
+        <v>14.8</v>
+      </c>
+      <c r="E344">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A345" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B345" t="b">
+        <v>0</v>
+      </c>
+      <c r="C345" t="s">
+        <v>12</v>
+      </c>
+      <c r="D345">
+        <v>10.9</v>
+      </c>
+      <c r="E345">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A346" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B346" t="b">
+        <v>0</v>
+      </c>
+      <c r="C346" t="s">
+        <v>13</v>
+      </c>
+      <c r="D346">
+        <v>13.7</v>
+      </c>
+      <c r="E346">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A347" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B347" t="b">
+        <v>0</v>
+      </c>
+      <c r="C347" t="s">
+        <v>14</v>
+      </c>
+      <c r="D347">
+        <v>13.5</v>
+      </c>
+      <c r="E347">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A348" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B348" t="b">
+        <v>0</v>
+      </c>
+      <c r="C348" t="s">
+        <v>15</v>
+      </c>
+      <c r="D348">
+        <v>14</v>
+      </c>
+      <c r="E348">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A349" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B349" t="b">
+        <v>0</v>
+      </c>
+      <c r="C349" t="s">
+        <v>16</v>
+      </c>
+      <c r="D349">
+        <v>13.9</v>
+      </c>
+      <c r="E349">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A350" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B350" t="b">
+        <v>0</v>
+      </c>
+      <c r="C350" t="s">
+        <v>17</v>
+      </c>
+      <c r="D350">
+        <v>12.9</v>
+      </c>
+      <c r="E350">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A351" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B351" t="b">
+        <v>0</v>
+      </c>
+      <c r="C351" t="s">
+        <v>18</v>
+      </c>
+      <c r="D351">
+        <v>14.6</v>
+      </c>
+      <c r="E351">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A352" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B352" t="b">
+        <v>0</v>
+      </c>
+      <c r="C352" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A353" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B353" t="b">
+        <v>0</v>
+      </c>
+      <c r="C353" t="s">
+        <v>20</v>
+      </c>
+      <c r="D353">
+        <v>12.8</v>
+      </c>
+      <c r="E353">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B354" t="b">
+        <v>0</v>
+      </c>
+      <c r="C354" t="s">
+        <v>21</v>
+      </c>
+      <c r="D354">
+        <v>15.1</v>
+      </c>
+      <c r="E354">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A355" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B355" t="b">
+        <v>0</v>
+      </c>
+      <c r="C355" t="s">
+        <v>22</v>
+      </c>
+      <c r="D355">
+        <v>11.3</v>
+      </c>
+      <c r="E355">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A356" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B356" t="b">
+        <v>0</v>
+      </c>
+      <c r="C356" t="s">
+        <v>23</v>
+      </c>
+      <c r="D356">
+        <v>14.1</v>
+      </c>
+      <c r="E356">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A357" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B357" t="b">
+        <v>0</v>
+      </c>
+      <c r="C357" t="s">
+        <v>24</v>
+      </c>
+      <c r="D357">
+        <v>13.7</v>
+      </c>
+      <c r="E357">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A358" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B358" t="b">
+        <v>0</v>
+      </c>
+      <c r="C358" t="s">
+        <v>25</v>
+      </c>
+      <c r="D358">
+        <v>9.6</v>
+      </c>
+      <c r="E358">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A359" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B359" t="b">
+        <v>0</v>
+      </c>
+      <c r="C359" t="s">
+        <v>26</v>
+      </c>
+      <c r="D359">
+        <v>14.8</v>
+      </c>
+      <c r="E359">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A360" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B360" t="b">
+        <v>0</v>
+      </c>
+      <c r="C360" t="s">
+        <v>27</v>
+      </c>
+      <c r="D360">
+        <v>15.4</v>
+      </c>
+      <c r="E360">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A361" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B361" t="b">
+        <v>0</v>
+      </c>
+      <c r="C361" t="s">
+        <v>28</v>
+      </c>
+      <c r="D361">
+        <v>16.2</v>
+      </c>
+      <c r="E361">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A362" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B362" t="b">
+        <v>0</v>
+      </c>
+      <c r="C362" t="s">
+        <v>29</v>
+      </c>
+      <c r="D362">
+        <v>13.9</v>
+      </c>
+      <c r="E362">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A363" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B363" t="b">
+        <v>0</v>
+      </c>
+      <c r="C363" t="s">
+        <v>30</v>
+      </c>
+      <c r="D363">
+        <v>12.2</v>
+      </c>
+      <c r="E363">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A364" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B364" t="b">
+        <v>0</v>
+      </c>
+      <c r="C364" t="s">
+        <v>31</v>
+      </c>
+      <c r="D364">
+        <v>12.8</v>
+      </c>
+      <c r="E364">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A365" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B365" t="b">
+        <v>0</v>
+      </c>
+      <c r="C365" t="s">
+        <v>32</v>
+      </c>
+      <c r="D365">
+        <v>11.8</v>
+      </c>
+      <c r="E365">
+        <v>11.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
